--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Periyapuliyur_13.389385_80.036223.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Periyapuliyur_13.389385_80.036223.xlsx
@@ -1514,6 +1514,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1521,6 +1526,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1528,6 +1538,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 2, 3A, 3B, 3C, 3D, 3E, 3F, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1535,6 +1550,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1542,11 +1562,21 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
           <t>24</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1, 10, 2A, 2B, 2C, 2D, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Periyapuliyur_13.389385_80.036223.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Periyapuliyur_13.389385_80.036223.xlsx
@@ -1586,6 +1586,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13A, 13B, 14, 15A, 15B, 16, 17, 18, 19, 2, 20, 21, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1593,6 +1598,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A1, 18A2, 18B, 19, 2, 20A, 20B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1600,6 +1610,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1607,6 +1622,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1614,6 +1634,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1621,6 +1646,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B1, 10B2, 2A, 2B, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1628,6 +1658,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 2, 3A1, 3A2, 3B, 4A, 4B, 5, 6, 7, 8, 9A, 9B, 9C1, 9C2</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1635,6 +1670,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13A, 13B, 14, 15, 2A, 2B, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1642,6 +1682,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 16, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1649,6 +1694,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1656,6 +1706,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1663,6 +1718,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 2, 3, 4A, 4B, 5A1, 5A2, 5B, 6A, 6B, 6C, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1670,6 +1730,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 3D, 4, 5, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1677,6 +1742,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>10A1A, 10A1B, 10A2, 10B, 11, 1A, 1B, 1C, 1D1, 1D2, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1684,6 +1754,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1691,6 +1766,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1698,6 +1778,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12A, 12B, 12C, 13A, 13B, 1A, 1B, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1705,6 +1790,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1712,6 +1802,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5A, 5B1, 5B2, 6, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1719,6 +1814,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 1A, 1B, 2A, 2B, 3, 4, 5A, 5B, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1726,6 +1826,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1733,6 +1838,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1740,6 +1850,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1747,6 +1862,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 2A, 2B, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1754,6 +1874,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>10A, 10B, 1A, 1B, 2A, 2B, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1761,6 +1886,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1768,6 +1898,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1775,6 +1910,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 3A, 3B, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1782,6 +1922,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1789,6 +1934,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1796,6 +1946,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1803,6 +1958,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 20A, 20B, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1810,6 +1970,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1817,6 +1982,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C1, 4C2, 4D, 5A1, 5A2, 5B, 5C, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1824,6 +1994,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1831,6 +2006,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1838,6 +2018,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1845,6 +2030,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1852,6 +2042,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2, 3, 4, 5A, 5B, 6A, 6B, 7A, 7B1, 7B2, 7B3, 7B4</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1859,6 +2054,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1866,6 +2066,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1873,6 +2078,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1880,11 +2090,21 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
           <t>64</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 3A, 3B1, 3B2, 4, 5A, 5B, 5C</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Periyapuliyur_13.389385_80.036223.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Periyapuliyur_13.389385_80.036223.xlsx
@@ -2114,6 +2114,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 1A, 1B, 2A, 2B, 3A, 3B, 3C, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2121,6 +2126,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18A, 18B, 18C, 2, 3, 4, 5, 6A, 6B, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2128,6 +2138,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23A, 23B, 24, 25, 26, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2135,6 +2150,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2142,6 +2162,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20A, 20B, 21, 22, 23, 24, 3, 4, 5, 6A, 6B1, 6B2, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2149,6 +2174,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 2A, 2B, 3, 4, 5A, 5B, 6A1, 6A2, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2156,6 +2186,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2163,6 +2198,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2170,11 +2210,21 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
           <t>73</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Periyapuliyur_13.389385_80.036223.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Periyapuliyur_13.389385_80.036223.xlsx
@@ -2234,6 +2234,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2241,6 +2246,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2248,6 +2258,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7A, 7B, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2255,6 +2270,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2262,6 +2282,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 2, 3, 4A, 4B, 5, 6A, 6B1, 6B2, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2269,6 +2294,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2276,6 +2306,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2283,6 +2318,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2290,6 +2330,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2297,6 +2342,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2304,6 +2354,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 11C, 11D, 11E, 11F, 11G, 11H, 12, 13, 14, 15, 16A, 16B, 17A, 17B, 17C, 18, 19, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2311,6 +2366,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11A, 11B, 12A, 12B, 12C, 12D, 12E, 13A, 13B, 13C, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2318,6 +2378,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 13, 14, 15, 16, 1A, 1B, 1C, 2A, 2B, 3A, 3B, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2325,6 +2390,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2332,6 +2402,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16A, 16B, 16C, 17, 18A, 18B, 19, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2339,6 +2414,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2346,6 +2426,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 16, 17, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2353,6 +2438,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2360,6 +2450,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 3, 4, 5, 6A, 6B, 6C, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2367,6 +2462,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 6C</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2374,6 +2474,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 1A, 1B, 2, 3, 4, 5, 6, 7A, 7B, 8, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2381,6 +2486,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12, 13, 14, 15, 16, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2388,6 +2498,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2395,6 +2510,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5A, 5B, 6, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2402,6 +2522,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2409,6 +2534,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A1, 15A2, 15B, 16, 17A1, 17A2, 17B, 17C, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2416,11 +2546,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2A1, 2A2, 2B, 3A, 3B, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 18, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
         </is>
       </c>
     </row>
